--- a/inputs/fr/template_input.xlsx
+++ b/inputs/fr/template_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\2025 studies\Nutrition\inputs\fr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modelling projects\Nutrition\inputs\fr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2027410-5F59-46F7-BA3B-055E59CB7B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CA4E561-712B-4030-A5D0-0000207471D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Données pop de l'année de ref" sheetId="1" r:id="rId1"/>
@@ -9833,7 +9833,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="GwWkUYuZLpGPcYgtHrvqwdqmIRieewOApjr2Jzw7aDBZEudwIGefxfsqW18d/7Q/u/na6JkcmZIyidDURdggEA==" saltValue="W56NtmcBCiVZlFdsy2Hn/A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dcwN/iJ4vQlKNfa0/yY1QEWXxnWy6KBjQSy6mA/hmkAKF0HcUWlnmLlNxN5Mbp1LAnqlDPtq4VOD1Q+Jmrz21Q==" saltValue="3KN8LseqWRhC4cHMCbc4zg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10758,7 +10758,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/04qBfB2LXZo7HtFmPj1LPped+ObhvR+PU5EslDj3mAD8daLiJo2Q5rfft5cqOXzEVyM5uBcGNs5cfF2smWOJw==" saltValue="WRgqiRStXdtHLPLlgwVf/A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="uxAk6BTdG8TF6sKS+UQOFs9g/iq4ann0JrbeYdyKBBmX5f8g5l7wOOQwvV6qvVr52W4b0UMvETA11Xu4sCN4Yw==" saltValue="d5al+0ZHAbOLTcigU4Jmpw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10911,7 +10911,7 @@
       <c r="C20" s="58"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="2AZeQvXCjoixjgLZQIAAMIwmaRjno00afXBlnAOjpqAr+L/5nl3vdmVxlyqZxegY0acx1Ra7nutzkZyc7gNc4Q==" saltValue="oHS/f7FlvqJkFUs96cmsoQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="+EJLq6EPIh851CheGHHqgeqDEKpi7RhkqZgeoQiOx6u6FnM4Rk2QT9mJg9sGAgI2JGCUSUtrOtL9+XO0zAWHeg==" saltValue="w+LHlYzF7iY8JgTe163LJg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -11009,7 +11009,7 @@
       <c r="A19" s="33"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="xFu/7WZGKf1ehHwcTv9ODA0xzYP7DyuMuCtlRjnli/0QNBwC+qBUG8bLw2hc//2GhSwJSc2ReMRvf1sr0ITRpA==" saltValue="4gRWWouWIBKY9xvBHRFKIA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PQuAqJ5rWXA87K6Jr7f2fWwDCWUygbhzr9i9cxMAlwK6Ps1/uDExrO3B7W2dQ1M6Ru5oVijWKqsID4hHqpUzow==" saltValue="e4KbHVJyEYbrimCPc1s7mg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -11119,7 +11119,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="qKeBugpUvNG7W9jVK4G3bb+ngG0/enCc1yMzgpbY+oixJNuQub7BG4WR8NFGJyoiKaxC1rZp4cJTm6Cv8E2H9w==" saltValue="KqHDyjMuUA1mRlkYi62XFQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="SsmpEKIFa5hLMZvo5jDYToiG3cUYWOnh14/ZrpATxv85DZ8pVWFFeeQoVTGsQ0CgZmdaBPEp7rfsz79wSR6FgQ==" saltValue="I5tqmti+ks1UE+ibXDkYjw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -12877,7 +12877,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="FnKf2MKHjSk8ePJcbytfjcCrOh53aldAJHnxLsgSNfVaqAc0ToN8nK+kwPxJIVVAoCQ5HIUQGnQr8Xoz3/L8Dw==" saltValue="eCTV8ZAXD8tkw6Fz0+qjJg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="LEmOleGROk58l2OwJTmiEpKU7Y7/TDDsHaF+PmNcZquhgVEURtSTBnOdnQKwV2k22bOWWLqJbUA1a0jJR3E38g==" saltValue="Ee20JzGMYqEytGN+rEgSqg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -12910,7 +12910,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="58fUo9rGMdLTgXOSRPv3chHsYAUk6sFpZA2DL8Z+P5XgCJkzOWlFgsNlWwVjXxDOgAHwaAYE6uuNLVKmOg679A==" saltValue="JAn56mlgvDqztYo6D4A80Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1+mwcTtRXZPz+ggMBROHbsCOU+Iy+s+tomBj0V43njH7tkFNM7D1CoImRJPD9NlbZMGjASJTp6ow1xcBWGl+4w==" saltValue="jb8rJb0CkcBrtnhFgKGBQA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13111,7 +13111,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Nx2StiEvxtfrfO66g1996Qrab1AOQUcaUQzqwdFbgAek5KdsvYvXPcT/UX6HMmctUzNpq+PK2Ktp1qTUqzIYhQ==" saltValue="CAC2rEQU7Hbdx9EuawuNUQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="CMEM5CL6PvEu9SfGMe+NwatUrG4yXIqQNhSHs/5OnyqmGokfiLHJ4NJaZcH414SWUsTPQJTTLz9tnH7rnGJWvQ==" saltValue="oGPrOiNTyYJJjx+KDzi3FQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -14921,7 +14921,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="WK6rcyeHabuEAYPkVzgFxnsAmxX53j777sP0RFPKnz6ncq99TYrQUmLv0GyV33Pup3zCv39oAffRZS69QgAvzA==" saltValue="VIZ3QQ/QT3ckZz2aRlnTgQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="hZDqbAR9fOIlPFOr7P4fT69IXJKXiamb03gBqCOPGzIjkOCVrXWKYGgUZf3MzQ2/ZYT84wnW/KCHAzmMus4Zbw==" saltValue="6f81ExCJNeERGtabHdM+WQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15732,7 +15732,7 @@
       <c r="L39" s="114"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="wvI2mN1UlZb91EZJEiEf6xVVPvKoVvSSn0gZCwuA6zvT/9XaEK52bnaYF0sgVi8JEIfz+Qs66YeDrXn8NunhgQ==" saltValue="BorqFwW0gp4OBDrutVFbTg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="hf6W2uJnllGmOP2NXCKZ2HsLn2atbaee6ZZXhUDRQOzGyVG41Lg2937prpS28dhoeHXVSkRiuFDANO3xYcDP+A==" saltValue="6RIrWokFCsLkluZSPQthjw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16125,7 +16125,7 @@
       <c r="L14" s="114"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OSdFuZ0SG/ukJBXRTL9y9hJ5mK2D5lg0OHN5u9T8dWxO4Yu8O/ur9wRFrYEm6TeKwMeMwHf8S80Wcgl/JwFcyA==" saltValue="HoBeZ8oVqPIc7y9o8eAYMQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="BeucgRtYxlv79nOfwO0liuvZ3gMiHzwjbCY4QX/a9ocgOP6ag3pjKNeJcuUhslhPkEtCR+mYgN8/DHJ9pJaapw==" saltValue="4Wzt0WTuEBq5JWZkn+V/Ug==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16854,7 +16854,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="hdbusW1EZXoBXXJfM4CzER6xfkfAot2tkwTKtkib5LKzcTSqbqA5NyU86RDckTbyeOwh65NvkQdOpbcmhVWfyA==" saltValue="AfU+3b4IiBmyZCUWpEuryA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bOymzAy1Z2febZHkrrT6Z31qDbNRUx7IogjFCNzDkVJiSmYkOLnh0xiSQ+WTuCj556wVuR7GCHp1+55ZSxQrrw==" saltValue="KBbKpRLT+jFDLDLiTdDX/w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -20651,7 +20651,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="T9GhEG+F13igFxubWu7A0SJL2tjIV6CptonmSucI0Zlrb66OUuELL9tsIh++GJEY1gSjpZIr1N5Lpn7Vft6AmA==" saltValue="d2l/HBtVEJP+dIPP+Az5Cw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="IugtfDvs/AUWCo8aQmoU8UNtM+DcMs/jX2xXuVDpCp9Tr2ngCWWQBDYQilF4BxujJpmetLTdHZU3jYQv50OIeQ==" saltValue="NxyUwmE9nMXzb8GoN6CcJw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B36:B38"/>
@@ -21798,7 +21798,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="tGfKGYnUZAdGek7c3SJxWObV0yTBJmTZkw0p45FmkxWsUHnlkJi8jh2T1y/oUQkKXNFo168YepTS4MQGwq3nIA==" saltValue="kfzbueRo8yvvikVTB+szfQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="CY8oykZHbp/OzTcIHeLfkLJRM+IVBIy59FHCiualF7QjCSk+2DAPiv4DiBwKK6STSZ163ZfhM4tdG8reHvtbfA==" saltValue="uozHMQvYQtKuQdP6HozfNA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -22739,7 +22739,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="9zRaYgRVGfKg95Gva+D9bjUVgMFlcAT4F6VRuTCPHTAv3WYpyg+4V2G7QaA2U0Axeu3UChgPOZMqVfnlQK21aQ==" saltValue="Fw/vLSKefFMvpnH2nWgbzQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="yvhlL/vFP0MgZ0+0s4lWts/vaGgv9FXatyd9HbkDuCZLznFOY3Pnmp0nw8PzkJW3oFne7YzAh8Z1/KmoorBPOQ==" saltValue="ZUsf82P+mp7RuD8Eqa54Qg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -23955,7 +23955,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pUkRqBazUeH4nxuKOrpXPxWRDvpkhvQ3KNwFH4f7UppQgA03jepI72kkem1Nou/O9BpyTyvVKzP71cSyrpJKew==" saltValue="Mi0Z0uQOzyzF6zkdTE8wFA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bQ7PrWUo/KOmmEV3ybEtl0uL3KNhw8w1m1U6Avb5JOJNXmoIxFsc9HuRXQq58xsLTGF/CLXQtqQAPpyZPbiQKg==" saltValue="Ul103DG5j4X19Umz/JM91A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -32090,7 +32090,7 @@
       <c r="I328" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Vw3gV12o0aUdFCevCe+YOtgJTJGfd6gh3ErMh7eNJGp6TNGi8sFFeWcSMMQf5kpnTmqCrQ/VFonyQ1p+zflm0w==" saltValue="hzKm3tmawfBy621bIPFFRQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="nulOikhlfZaHEN/FXMbjHrzQYe+e4PIcoKZm2ImVIrgZRQOshbdxgi9rH7rWN/K5MariGuXto7hxo74Ajiof1Q==" saltValue="YbsgN3MVfoCu/9X7uf22AA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -34780,7 +34780,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="5JS4/ztL2eQleqg1BQPkUV4+5m9WpoEQ3bnRkgXsX06s4BwvMX2PTJAPsmnJv/ubVcZqQmbBkhFU+XGv7woN2g==" saltValue="6XKXEla+R4wE8RTmuplZXQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PgsS/SMDicKw7QlGujOj+R0FkXjgtSD1TUVeWOe04fqc8RFvjgMocGowqov4ZqYINuFiVRcB6/R1UiEDy2BGsA==" saltValue="PYwkBpY33YqMlY7fSDuwPA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -35062,7 +35062,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bdEhb2krC4lYvvvberRAba6+uIJs7LpEPpT0w3mFOQUviZ5GJj8xc62PmhlEJ1cYpTsKL4cfELpx7dO+/e5ayA==" saltValue="INssIcmmJ2W3IPNDZaBhbg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="UTDC1EM/AUXLnasQOkpBIGIDCQvPO24RrosnCwdFOUm0V4gQptkquANvRlHuYtHHSxzyiOhilD4D/mrH3v/ikQ==" saltValue="VqWyNdOtRQF4DU6wVxqV4Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -38922,7 +38922,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="R0Igyf9KMZUZ66rbyivbLqgdJjddJe8Qib9zNdRjfOZW78q5n51V7HsNVtmk8IsQypKPa9fN6IWrl+nY/k3n5g==" saltValue="geA+8+mHHOMYw3dop0Mmfg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="F5X1OAf+5IxqmwzgLGc2vAA32mXbs9TzMBhBFTZeJrPZyKI9nPvoSAy2DO6ozMTilTeURlb7A9+Iv2yl9/6Wsg==" saltValue="gG2DSjlpPQpGyS5SBYwLSA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -39562,7 +39562,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ZVd8/cku1ilm71OsvJJ9ThNtBXafv2fMm3ficaMElJMUKpgLYtN+ZPCw1ZFRHoDNjNCgBR0AAS1Y48OD+2ci3A==" saltValue="YeXg4C33HXuMpq9ckww47g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="oP5imiJwu6S71f2KvCPPDNiZOmB110uPpj39fEH9Shv1iTXG0VqJyWZ1OaxuFHA5QxCSr9C/leRxavcpDPA45w==" saltValue="3E5GhLELRd8VapDtnWXjug==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -39889,7 +39889,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="57BodIup0lA4l5bd4dkMiyKKdO30H6c1xHRvho+wh6q7FlYooKHypkgqY378BcGQl8ZjhwH4NzG73tE0MZVcbQ==" saltValue="PZMmE4oSrCcIznF5z1mNKg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="yMBLEpCar3CmvbaMKvZxWNsBUyxHywhWMatu5erT2XAAEfzk0Z9mchUJCpz/8pwagIZKYFS61+9iX6jF9z+tYA==" saltValue="MKg3Oz+D6Bor1CVOr+GBag==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -40242,7 +40242,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Hti5tKWobsN7wLbxk00EgVggM4Kw/1JV+9RK0FSaiYPXg3hNF5h8+mUTqtrhDv7rQ3v5cByC18Vibu7aG2SIiQ==" saltValue="aOqZR5O5FjTHvtLexIeFkw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HvEiI1d8ysl9ouXg/9rafS6PEPVNBwROc0NR5sWLQl6E+cXfKC25bOSOgvmLiyBxbS/gpm/3WscpNb78MetMwA==" saltValue="UTlRVLzYsGwQB+0wYmYwfw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -40358,7 +40358,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6tUp/8OehSR29t1rn4ZqxbPluIpO6lGmKglDQiBiMJ5LbOlvX9cjs1uqWhv1Df1ioVNjhHTDc3sYGZTyr5BQ0g==" saltValue="gU3iYpJpMFqPaOiDY9qVrg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OTLoMUtLVkssMLPPQbo9K6FslTjR+dURRfaO6ZteRsgqemiSfQ5h50+Earw1QlTvQR1LHKyeL7KzD+91KeFrpg==" saltValue="IYrUOwjIgdNltyasZu1KAg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -40559,7 +40559,7 @@
       <c r="K14" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="5sPYyvJWUZdBghA1viBzs4A7Iona8edbMVskk7qbE7BU0o2yEx3MqGjQXk8Feyd47COUYgQBsu2PvAma1iZGow==" saltValue="03nGDHYDXbFvJYNtytSJQA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="uQvi8r+sBVJdz1GvDQz6t/ZFi+JKEHmb+e3v5L2QfvXDRA4z2aCBzp0R4bKgK6AkyyN33EsSofLCdp5v0QEi5g==" saltValue="cy3TmwpBPIsP8GGyxMJErQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait"/>
 </worksheet>
@@ -41022,7 +41022,7 @@
       <c r="O22" s="107"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="o1ukkEk1hAHJSvisQdekXFSsC4ZE6w+0DyZV2pbxskwY19uHP8YVAiVtidQbtefcmmT8p6LiTMt66iKhf9glYA==" saltValue="7IenQE26z2spr4+cKQHhFA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="z+MsKv91ketLRJ9bMViir1KrjT2ZoXn7n48WIuWoVPC13LFdhCI6otQlW+cyKtKkIH0dMN+x5SOJauOxbdTcEw==" saltValue="lwKUhYoriG36B55UuGnBUg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -41281,7 +41281,7 @@
       <c r="E21" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vqoBVwjPyAPDI3l4mNXQ1nbgZ6Z0hlakWZ8sFPqRyAPo0f8SoLHYtcZlCZwVe16ii3syF3wLr4VjdqlTEKH8ZQ==" saltValue="IwbUMT2F8T/NvHOz1o7Q3w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ptWsWEgCzg+xrHm4E+/+OdfodL7o3wVMdtFWbB3p8SCEQosohpLadHvkkZp1Ed86Y5yIr6t5FFVDPTNg1qon5g==" saltValue="htWV3GMnOgh59x9ApapSjA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -41340,7 +41340,7 @@
       <c r="D3" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="fISGtLaTU6jc3SEZV7GPCgv/ufk/l5UVSbXP61XSqP0fk8eMYo0HFWyLcACFvffILXU2/0tePt3SQrw/nHly1g==" saltValue="bQMa+R0doCPCE86eTP+DPQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="hSKsXJavcaNQTucOkUjqccLGhtROg+y9P6Y3rK30QkuoaSy0oudA07nPheMj0KIKOC1SxTHFi+GKGIJ9c3WVxQ==" saltValue="dWiWxuN0FRokhYW0cT8bKg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
